--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,6 +1525,51 @@
         <v>32</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-06-13 11:55:02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-06-13 11:55:03</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-06-13 11:55:03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1570,6 +1570,321 @@
         <v>30.4</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:36:26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:36:26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:36:27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:37:27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:37:28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:37:28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:38:28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:38:28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:38:29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:58:18</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:58:18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:58:18</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:59:19</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:59:19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-06-16 02:59:19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:00:43</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:00:43</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:00:43</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:00:43</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Quetta</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:00:43</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:00:43</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
